--- a/research/traditional_assets/database/data/brazil/brazil_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_reinsurance.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0601</v>
-      </c>
-      <c r="F2">
-        <v>0.2</v>
+        <v>0.0712</v>
       </c>
       <c r="G2">
-        <v>-0.1806134969325153</v>
+        <v>-0.1367616033755274</v>
       </c>
       <c r="H2">
-        <v>-0.1806134969325153</v>
+        <v>-0.1367616033755274</v>
       </c>
       <c r="I2">
-        <v>-0.1458282208588957</v>
+        <v>-0.13792194092827</v>
       </c>
       <c r="J2">
-        <v>-0.1458282208588957</v>
+        <v>-0.13792194092827</v>
       </c>
       <c r="K2">
-        <v>-183.6</v>
+        <v>-177.8</v>
       </c>
       <c r="L2">
-        <v>-0.1126380368098159</v>
+        <v>-0.09377637130801689</v>
       </c>
       <c r="M2">
-        <v>4.58</v>
+        <v>0.002</v>
       </c>
       <c r="N2">
-        <v>0.005061892130857649</v>
+        <v>4.966476285075739e-06</v>
       </c>
       <c r="O2">
-        <v>-0.02494553376906318</v>
+        <v>-1.124859392575928e-05</v>
       </c>
       <c r="P2">
-        <v>4.58</v>
+        <v>0.002</v>
       </c>
       <c r="Q2">
-        <v>0.005061892130857649</v>
+        <v>4.966476285075739e-06</v>
       </c>
       <c r="R2">
-        <v>-0.02494553376906318</v>
+        <v>-1.124859392575928e-05</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="V2">
-        <v>0.01270999115826702</v>
+        <v>0.02830891482493171</v>
       </c>
       <c r="W2">
-        <v>-0.2115451088835119</v>
+        <v>-0.2394935344827586</v>
       </c>
       <c r="X2">
-        <v>0.1270368441449114</v>
+        <v>0.1946171397599664</v>
       </c>
       <c r="Y2">
-        <v>-0.3385819530284233</v>
+        <v>-0.434110674242725</v>
       </c>
       <c r="Z2">
-        <v>1.886552238978715</v>
+        <v>2.136338028169014</v>
       </c>
       <c r="AA2">
-        <v>-0.2751125565676323</v>
+        <v>-0.2946478873239436</v>
       </c>
       <c r="AB2">
-        <v>0.1135058553729533</v>
+        <v>0.1544415990352837</v>
       </c>
       <c r="AC2">
-        <v>-0.3886184119405856</v>
+        <v>-0.4490894863592274</v>
       </c>
       <c r="AD2">
-        <v>156.6</v>
+        <v>172.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>156.6</v>
+        <v>172.4</v>
       </c>
       <c r="AG2">
-        <v>145.1</v>
+        <v>161</v>
       </c>
       <c r="AH2">
-        <v>0.1475409836065574</v>
+        <v>0.299773952356112</v>
       </c>
       <c r="AI2">
-        <v>0.1741935483870968</v>
+        <v>0.1851374570446735</v>
       </c>
       <c r="AJ2">
-        <v>0.1382036384417564</v>
+        <v>0.2856129146709242</v>
       </c>
       <c r="AK2">
-        <v>0.1634929577464789</v>
+        <v>0.1750380517503805</v>
       </c>
       <c r="AL2">
-        <v>9.210000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="AM2">
-        <v>9.210000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="AN2">
-        <v>-0.6644039032668647</v>
+        <v>-0.6651234567901235</v>
       </c>
       <c r="AO2">
-        <v>-25.80890336590662</v>
+        <v>-8.924914675767917</v>
       </c>
       <c r="AP2">
-        <v>-0.6156130674586339</v>
+        <v>-0.621141975308642</v>
       </c>
       <c r="AQ2">
-        <v>-25.80890336590662</v>
+        <v>-8.924914675767917</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0601</v>
-      </c>
-      <c r="F3">
-        <v>0.2</v>
+        <v>0.0712</v>
       </c>
       <c r="G3">
-        <v>-0.1806134969325153</v>
+        <v>-0.1367616033755274</v>
       </c>
       <c r="H3">
-        <v>-0.1806134969325153</v>
+        <v>-0.1367616033755274</v>
       </c>
       <c r="I3">
-        <v>-0.1458282208588957</v>
+        <v>-0.13792194092827</v>
       </c>
       <c r="J3">
-        <v>-0.1458282208588957</v>
+        <v>-0.13792194092827</v>
       </c>
       <c r="K3">
-        <v>-183.6</v>
+        <v>-177.8</v>
       </c>
       <c r="L3">
-        <v>-0.1126380368098159</v>
+        <v>-0.09377637130801689</v>
       </c>
       <c r="M3">
-        <v>4.58</v>
+        <v>0.002</v>
       </c>
       <c r="N3">
-        <v>0.005061892130857649</v>
+        <v>4.966476285075739e-06</v>
       </c>
       <c r="O3">
-        <v>-0.02494553376906318</v>
+        <v>-1.124859392575928e-05</v>
       </c>
       <c r="P3">
-        <v>4.58</v>
+        <v>0.002</v>
       </c>
       <c r="Q3">
-        <v>0.005061892130857649</v>
+        <v>4.966476285075739e-06</v>
       </c>
       <c r="R3">
-        <v>-0.02494553376906318</v>
+        <v>-1.124859392575928e-05</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="V3">
-        <v>0.01270999115826702</v>
+        <v>0.02830891482493171</v>
       </c>
       <c r="W3">
-        <v>-0.2115451088835119</v>
+        <v>-0.2394935344827586</v>
       </c>
       <c r="X3">
-        <v>0.1270368441449114</v>
+        <v>0.1946171397599664</v>
       </c>
       <c r="Y3">
-        <v>-0.3385819530284233</v>
+        <v>-0.434110674242725</v>
       </c>
       <c r="Z3">
-        <v>1.886552238978715</v>
+        <v>2.136338028169014</v>
       </c>
       <c r="AA3">
-        <v>-0.2751125565676323</v>
+        <v>-0.2946478873239436</v>
       </c>
       <c r="AB3">
-        <v>0.1135058553729533</v>
+        <v>0.1544415990352837</v>
       </c>
       <c r="AC3">
-        <v>-0.3886184119405856</v>
+        <v>-0.4490894863592274</v>
       </c>
       <c r="AD3">
-        <v>156.6</v>
+        <v>172.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>156.6</v>
+        <v>172.4</v>
       </c>
       <c r="AG3">
-        <v>145.1</v>
+        <v>161</v>
       </c>
       <c r="AH3">
-        <v>0.1475409836065574</v>
+        <v>0.299773952356112</v>
       </c>
       <c r="AI3">
-        <v>0.1741935483870968</v>
+        <v>0.1851374570446735</v>
       </c>
       <c r="AJ3">
-        <v>0.1382036384417564</v>
+        <v>0.2856129146709242</v>
       </c>
       <c r="AK3">
-        <v>0.1634929577464789</v>
+        <v>0.1750380517503805</v>
       </c>
       <c r="AL3">
-        <v>9.210000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="AM3">
-        <v>9.210000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="AN3">
-        <v>-0.6644039032668647</v>
+        <v>-0.6651234567901235</v>
       </c>
       <c r="AO3">
-        <v>-25.80890336590662</v>
+        <v>-8.924914675767917</v>
       </c>
       <c r="AP3">
-        <v>-0.6156130674586339</v>
+        <v>-0.621141975308642</v>
       </c>
       <c r="AQ3">
-        <v>-25.80890336590662</v>
+        <v>-8.924914675767917</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_reinsurance.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0712</v>
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="E2">
+        <v>-0.49</v>
       </c>
       <c r="G2">
-        <v>-0.1367616033755274</v>
+        <v>-0.03530803018357923</v>
       </c>
       <c r="H2">
-        <v>-0.1367616033755274</v>
+        <v>-0.03530803018357923</v>
       </c>
       <c r="I2">
-        <v>-0.13792194092827</v>
+        <v>0.08756616736118933</v>
       </c>
       <c r="J2">
-        <v>-0.13792194092827</v>
+        <v>0.08756616736118933</v>
       </c>
       <c r="K2">
-        <v>-177.8</v>
+        <v>7.53</v>
       </c>
       <c r="L2">
-        <v>-0.09377637130801689</v>
+        <v>0.00424034238089875</v>
       </c>
       <c r="M2">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>4.966476285075739e-06</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-1.124859392575928e-05</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>4.966476285075739e-06</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-1.124859392575928e-05</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>11.4</v>
+        <v>1.58</v>
       </c>
       <c r="V2">
-        <v>0.02830891482493171</v>
+        <v>0.002108916177255739</v>
       </c>
       <c r="W2">
-        <v>-0.2394935344827586</v>
+        <v>0.0099235635213495</v>
       </c>
       <c r="X2">
-        <v>0.1946171397599664</v>
+        <v>0.1533408805588014</v>
       </c>
       <c r="Y2">
-        <v>-0.434110674242725</v>
+        <v>-0.1434173170374519</v>
       </c>
       <c r="Z2">
-        <v>2.136338028169014</v>
+        <v>1.930637095020657</v>
       </c>
       <c r="AA2">
-        <v>-0.2946478873239436</v>
+        <v>0.1690584909762992</v>
       </c>
       <c r="AB2">
-        <v>0.1544415990352837</v>
+        <v>0.1315122730861081</v>
       </c>
       <c r="AC2">
-        <v>-0.4490894863592274</v>
+        <v>0.03754621789019116</v>
       </c>
       <c r="AD2">
-        <v>172.4</v>
+        <v>214.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>172.4</v>
+        <v>214.3</v>
       </c>
       <c r="AG2">
-        <v>161</v>
+        <v>212.72</v>
       </c>
       <c r="AH2">
-        <v>0.299773952356112</v>
+        <v>0.2224182667358588</v>
       </c>
       <c r="AI2">
-        <v>0.1851374570446735</v>
+        <v>0.2042508577964163</v>
       </c>
       <c r="AJ2">
-        <v>0.2856129146709242</v>
+        <v>0.2211410512308716</v>
       </c>
       <c r="AK2">
-        <v>0.1750380517503805</v>
+        <v>0.2030507244993414</v>
       </c>
       <c r="AL2">
-        <v>29.3</v>
+        <v>26.8</v>
       </c>
       <c r="AM2">
-        <v>29.3</v>
+        <v>26.8</v>
       </c>
       <c r="AN2">
-        <v>-0.6651234567901235</v>
+        <v>1.361499364675985</v>
       </c>
       <c r="AO2">
-        <v>-8.924914675767917</v>
+        <v>5.802238805970149</v>
       </c>
       <c r="AP2">
-        <v>-0.621141975308642</v>
+        <v>1.35146124523507</v>
       </c>
       <c r="AQ2">
-        <v>-8.924914675767917</v>
+        <v>5.802238805970149</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0712</v>
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="E3">
+        <v>-0.49</v>
       </c>
       <c r="G3">
-        <v>-0.1367616033755274</v>
+        <v>-0.03530803018357923</v>
       </c>
       <c r="H3">
-        <v>-0.1367616033755274</v>
+        <v>-0.03530803018357923</v>
       </c>
       <c r="I3">
-        <v>-0.13792194092827</v>
+        <v>0.08756616736118933</v>
       </c>
       <c r="J3">
-        <v>-0.13792194092827</v>
+        <v>0.08756616736118933</v>
       </c>
       <c r="K3">
-        <v>-177.8</v>
+        <v>7.53</v>
       </c>
       <c r="L3">
-        <v>-0.09377637130801689</v>
+        <v>0.00424034238089875</v>
       </c>
       <c r="M3">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>4.966476285075739e-06</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-1.124859392575928e-05</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>4.966476285075739e-06</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-1.124859392575928e-05</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>11.4</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
-        <v>0.02830891482493171</v>
+        <v>0.002108916177255739</v>
       </c>
       <c r="W3">
-        <v>-0.2394935344827586</v>
+        <v>0.0099235635213495</v>
       </c>
       <c r="X3">
-        <v>0.1946171397599664</v>
+        <v>0.1533408805588014</v>
       </c>
       <c r="Y3">
-        <v>-0.434110674242725</v>
+        <v>-0.1434173170374519</v>
       </c>
       <c r="Z3">
-        <v>2.136338028169014</v>
+        <v>1.930637095020657</v>
       </c>
       <c r="AA3">
-        <v>-0.2946478873239436</v>
+        <v>0.1690584909762992</v>
       </c>
       <c r="AB3">
-        <v>0.1544415990352837</v>
+        <v>0.1315122730861081</v>
       </c>
       <c r="AC3">
-        <v>-0.4490894863592274</v>
+        <v>0.03754621789019116</v>
       </c>
       <c r="AD3">
-        <v>172.4</v>
+        <v>214.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>172.4</v>
+        <v>214.3</v>
       </c>
       <c r="AG3">
-        <v>161</v>
+        <v>212.72</v>
       </c>
       <c r="AH3">
-        <v>0.299773952356112</v>
+        <v>0.2224182667358588</v>
       </c>
       <c r="AI3">
-        <v>0.1851374570446735</v>
+        <v>0.2042508577964163</v>
       </c>
       <c r="AJ3">
-        <v>0.2856129146709242</v>
+        <v>0.2211410512308716</v>
       </c>
       <c r="AK3">
-        <v>0.1750380517503805</v>
+        <v>0.2030507244993414</v>
       </c>
       <c r="AL3">
-        <v>29.3</v>
+        <v>26.8</v>
       </c>
       <c r="AM3">
-        <v>29.3</v>
+        <v>26.8</v>
       </c>
       <c r="AN3">
-        <v>-0.6651234567901235</v>
+        <v>1.361499364675985</v>
       </c>
       <c r="AO3">
-        <v>-8.924914675767917</v>
+        <v>5.802238805970149</v>
       </c>
       <c r="AP3">
-        <v>-0.621141975308642</v>
+        <v>1.35146124523507</v>
       </c>
       <c r="AQ3">
-        <v>-8.924914675767917</v>
+        <v>5.802238805970149</v>
       </c>
     </row>
   </sheetData>
